--- a/media/batchfiles/batch_report_OSI.xlsx
+++ b/media/batchfiles/batch_report_OSI.xlsx
@@ -416,42 +416,41 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AG3"/>
+  <dimension ref="A1:AF3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
-    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="10" customWidth="1" min="2" max="2"/>
     <col width="17" customWidth="1" min="3" max="3"/>
     <col width="16" customWidth="1" min="4" max="4"/>
     <col width="15" customWidth="1" min="5" max="5"/>
     <col width="13" customWidth="1" min="6" max="6"/>
-    <col width="12" customWidth="1" min="7" max="7"/>
-    <col width="9" customWidth="1" min="8" max="8"/>
-    <col width="17" customWidth="1" min="9" max="9"/>
-    <col width="20" customWidth="1" min="10" max="10"/>
-    <col width="27" customWidth="1" min="11" max="11"/>
-    <col width="20" customWidth="1" min="12" max="12"/>
-    <col width="15" customWidth="1" min="13" max="13"/>
-    <col width="13" customWidth="1" min="14" max="14"/>
-    <col width="14" customWidth="1" min="15" max="15"/>
-    <col width="17" customWidth="1" min="16" max="16"/>
-    <col width="19" customWidth="1" min="17" max="17"/>
-    <col width="14" customWidth="1" min="18" max="18"/>
-    <col width="17" customWidth="1" min="19" max="19"/>
-    <col width="18" customWidth="1" min="20" max="20"/>
-    <col width="16" customWidth="1" min="21" max="21"/>
-    <col width="17" customWidth="1" min="22" max="22"/>
-    <col width="20" customWidth="1" min="23" max="23"/>
-    <col width="22" customWidth="1" min="24" max="24"/>
-    <col width="18" customWidth="1" min="25" max="25"/>
-    <col width="11" customWidth="1" min="26" max="26"/>
-    <col width="16" customWidth="1" min="27" max="27"/>
-    <col width="20" customWidth="1" min="28" max="28"/>
-    <col width="19" customWidth="1" min="29" max="29"/>
-    <col width="16" customWidth="1" min="30" max="30"/>
-    <col width="12" customWidth="1" min="31" max="31"/>
-    <col width="18" customWidth="1" min="32" max="32"/>
-    <col width="27" customWidth="1" min="33" max="33"/>
+    <col width="9" customWidth="1" min="7" max="7"/>
+    <col width="17" customWidth="1" min="8" max="8"/>
+    <col width="20" customWidth="1" min="9" max="9"/>
+    <col width="27" customWidth="1" min="10" max="10"/>
+    <col width="20" customWidth="1" min="11" max="11"/>
+    <col width="15" customWidth="1" min="12" max="12"/>
+    <col width="13" customWidth="1" min="13" max="13"/>
+    <col width="14" customWidth="1" min="14" max="14"/>
+    <col width="17" customWidth="1" min="15" max="15"/>
+    <col width="19" customWidth="1" min="16" max="16"/>
+    <col width="14" customWidth="1" min="17" max="17"/>
+    <col width="17" customWidth="1" min="18" max="18"/>
+    <col width="18" customWidth="1" min="19" max="19"/>
+    <col width="16" customWidth="1" min="20" max="20"/>
+    <col width="17" customWidth="1" min="21" max="21"/>
+    <col width="20" customWidth="1" min="22" max="22"/>
+    <col width="22" customWidth="1" min="23" max="23"/>
+    <col width="18" customWidth="1" min="24" max="24"/>
+    <col width="11" customWidth="1" min="25" max="25"/>
+    <col width="16" customWidth="1" min="26" max="26"/>
+    <col width="20" customWidth="1" min="27" max="27"/>
+    <col width="19" customWidth="1" min="28" max="28"/>
+    <col width="16" customWidth="1" min="29" max="29"/>
+    <col width="12" customWidth="1" min="30" max="30"/>
+    <col width="18" customWidth="1" min="31" max="31"/>
+    <col width="27" customWidth="1" min="32" max="32"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -487,135 +486,130 @@
       </c>
       <c r="G1" t="inlineStr">
         <is>
-          <t>Company</t>
+          <t>Vendor</t>
         </is>
       </c>
       <c r="H1" t="inlineStr">
         <is>
-          <t>Vendor</t>
+          <t>BillingCurrency</t>
         </is>
       </c>
       <c r="I1" t="inlineStr">
         <is>
-          <t>BillingCurrency</t>
+          <t>Remittance Address</t>
         </is>
       </c>
       <c r="J1" t="inlineStr">
         <is>
-          <t>Remittance Address</t>
+          <t>Billing Name</t>
         </is>
       </c>
       <c r="K1" t="inlineStr">
         <is>
-          <t>Billing Name</t>
+          <t>Billing Address</t>
         </is>
       </c>
       <c r="L1" t="inlineStr">
         <is>
-          <t>Billing Address</t>
+          <t>Billing State</t>
         </is>
       </c>
       <c r="M1" t="inlineStr">
         <is>
-          <t>Billing State</t>
+          <t>Billing Zip</t>
         </is>
       </c>
       <c r="N1" t="inlineStr">
         <is>
-          <t>Billing Zip</t>
+          <t>Billing City</t>
         </is>
       </c>
       <c r="O1" t="inlineStr">
         <is>
-          <t>Billing City</t>
+          <t>Billing Country</t>
         </is>
       </c>
       <c r="P1" t="inlineStr">
         <is>
-          <t>Billing Country</t>
+          <t>Billing Attention</t>
         </is>
       </c>
       <c r="Q1" t="inlineStr">
         <is>
-          <t>Billing Attention</t>
+          <t>Billing Date</t>
         </is>
       </c>
       <c r="R1" t="inlineStr">
         <is>
-          <t>Billing Date</t>
+          <t>Remittance Name</t>
         </is>
       </c>
       <c r="S1" t="inlineStr">
         <is>
-          <t>Remittance Name</t>
+          <t>Remittance State</t>
         </is>
       </c>
       <c r="T1" t="inlineStr">
         <is>
-          <t>Remittance State</t>
+          <t>Remittance Zip</t>
         </is>
       </c>
       <c r="U1" t="inlineStr">
         <is>
-          <t>Remittance Zip</t>
+          <t>Remittance City</t>
         </is>
       </c>
       <c r="V1" t="inlineStr">
         <is>
-          <t>Remittance City</t>
+          <t>Remittance Country</t>
         </is>
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Remittance Country</t>
+          <t>Remittance Attention</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">
         <is>
-          <t>Remittance Attention</t>
+          <t>Remittance Notes</t>
         </is>
       </c>
       <c r="Y1" t="inlineStr">
         <is>
-          <t>Remittance Notes</t>
+          <t>Vendor ID</t>
         </is>
       </c>
       <c r="Z1" t="inlineStr">
         <is>
-          <t>Vendor ID</t>
+          <t>Batch Approved</t>
         </is>
       </c>
       <c r="AA1" t="inlineStr">
         <is>
-          <t>Batch Approved</t>
+          <t>Bill approved date</t>
         </is>
       </c>
       <c r="AB1" t="inlineStr">
         <is>
-          <t>Bill approved date</t>
+          <t>Batch Approved By</t>
         </is>
       </c>
       <c r="AC1" t="inlineStr">
         <is>
-          <t>Batch Approved By</t>
+          <t>Baseline Notes</t>
         </is>
       </c>
       <c r="AD1" t="inlineStr">
         <is>
-          <t>Baseline Notes</t>
+          <t>Net Amount</t>
         </is>
       </c>
       <c r="AE1" t="inlineStr">
         <is>
-          <t>Net Amount</t>
+          <t>bill_date_parsed</t>
         </is>
       </c>
       <c r="AF1" t="inlineStr">
-        <is>
-          <t>bill_date_parsed</t>
-        </is>
-      </c>
-      <c r="AG1" t="inlineStr">
         <is>
           <t>Uploaded by</t>
         </is>
@@ -654,93 +648,88 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>OneSmarter</t>
+          <t>Verizon</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Verizon</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>USD</t>
+          <t>PO BOX 16810</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>PO BOX 16810</t>
+          <t>BUILD-A-BEAR WORKSHOP INC</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>BUILD-A-BEAR WORKSHOP INC</t>
+          <t>7293 BEECHMONT AVE</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>7293 BEECHMONT AVE</t>
+          <t>OH</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>OH</t>
+          <t>45230-4125</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>45230-4125</t>
+          <t>CINCINNATI</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>CINCINNATI</t>
-        </is>
-      </c>
-      <c r="P2" t="inlineStr">
-        <is>
           <t>United States</t>
         </is>
       </c>
+      <c r="S2" t="inlineStr">
+        <is>
+          <t>NJ</t>
+        </is>
+      </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>OX</t>
+          <t>07101-6810</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>16810</t>
+          <t>NEWARK</t>
         </is>
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>PO B</t>
-        </is>
-      </c>
-      <c r="W2" t="inlineStr">
-        <is>
           <t>United States</t>
         </is>
       </c>
-      <c r="AA2" t="inlineStr">
+      <c r="Z2" t="inlineStr">
         <is>
           <t>Approved</t>
         </is>
       </c>
-      <c r="AB2" s="1" t="n">
-        <v>46056.34576601609</v>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Admin</t>
-        </is>
-      </c>
-      <c r="AE2" t="inlineStr">
+      <c r="AA2" s="1" t="n">
+        <v>46108.5328027788</v>
+      </c>
+      <c r="AB2" t="inlineStr">
+        <is>
+          <t>Client Admin</t>
+        </is>
+      </c>
+      <c r="AD2" t="inlineStr">
         <is>
           <t>5499.63</t>
         </is>
       </c>
-      <c r="AG2" t="inlineStr">
+      <c r="AF2" t="inlineStr">
         <is>
           <t>grddeveloper.py@gmail.com</t>
         </is>
@@ -749,12 +738,12 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>July 15 2025</t>
+          <t>May 15 2024</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>August 14 2025</t>
+          <t>Past</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -764,12 +753,12 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>6118585051</t>
+          <t>9964213310</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>$2704.51</t>
+          <t>$2696.49</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -779,93 +768,88 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>OneSmarter</t>
+          <t>Verizon</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Verizon</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>USD</t>
+          <t>PO BOX 16810</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>PO BOX 16810</t>
+          <t>BUILD-A-BEAR WORKSHOP INC</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>BUILD-A-BEAR WORKSHOP INC</t>
+          <t>7293 BEECHMONT AVE</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>7293 BEECHMONT AVE</t>
+          <t>OH</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>OH</t>
+          <t>45230-4125</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>45230-4125</t>
+          <t>CINCINNATI</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>CINCINNATI</t>
-        </is>
-      </c>
-      <c r="P3" t="inlineStr">
-        <is>
           <t>United States</t>
         </is>
       </c>
+      <c r="S3" t="inlineStr">
+        <is>
+          <t>OX</t>
+        </is>
+      </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>OX</t>
+          <t>16810</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>16810</t>
+          <t>PO B</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>PO B</t>
-        </is>
-      </c>
-      <c r="W3" t="inlineStr">
-        <is>
           <t>United States</t>
         </is>
       </c>
-      <c r="AA3" t="inlineStr">
+      <c r="Z3" t="inlineStr">
         <is>
           <t>Approved</t>
         </is>
       </c>
-      <c r="AB3" s="1" t="n">
-        <v>46056.35169982485</v>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Admin</t>
-        </is>
-      </c>
-      <c r="AE3" t="inlineStr">
-        <is>
-          <t>2704.51</t>
-        </is>
-      </c>
-      <c r="AG3" t="inlineStr">
+      <c r="AA3" s="1" t="n">
+        <v>46108.53636556549</v>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>Client Admin</t>
+        </is>
+      </c>
+      <c r="AD3" t="inlineStr">
+        <is>
+          <t>2761.63</t>
+        </is>
+      </c>
+      <c r="AF3" t="inlineStr">
         <is>
           <t>grddeveloper.py@gmail.com</t>
         </is>

--- a/media/batchfiles/batch_report_OSI.xlsx
+++ b/media/batchfiles/batch_report_OSI.xlsx
@@ -416,10 +416,10 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AF3"/>
+  <dimension ref="A1:AF2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="13" customWidth="1" min="1" max="1"/>
     <col width="10" customWidth="1" min="2" max="2"/>
     <col width="17" customWidth="1" min="3" max="3"/>
     <col width="16" customWidth="1" min="4" max="4"/>
@@ -429,7 +429,7 @@
     <col width="17" customWidth="1" min="8" max="8"/>
     <col width="20" customWidth="1" min="9" max="9"/>
     <col width="27" customWidth="1" min="10" max="10"/>
-    <col width="20" customWidth="1" min="11" max="11"/>
+    <col width="17" customWidth="1" min="11" max="11"/>
     <col width="15" customWidth="1" min="12" max="12"/>
     <col width="13" customWidth="1" min="13" max="13"/>
     <col width="14" customWidth="1" min="14" max="14"/>
@@ -618,12 +618,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>June 15 2024</t>
+          <t>Jan 15 2024</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Past</t>
+          <t>02/14/24</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -633,12 +633,12 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>9966671861</t>
+          <t>9954280341</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>$2696.49</t>
+          <t>34.56</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -666,26 +666,6 @@
           <t>BUILD-A-BEAR WORKSHOP INC</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>7293 BEECHMONT AVE</t>
-        </is>
-      </c>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>OH</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>45230-4125</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>CINCINNATI</t>
-        </is>
-      </c>
       <c r="O2" t="inlineStr">
         <is>
           <t>United States</t>
@@ -693,17 +673,17 @@
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>NJ</t>
+          <t>OX</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>07101-6810</t>
+          <t>16810</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>NEWARK</t>
+          <t>PO B</t>
         </is>
       </c>
       <c r="V2" t="inlineStr">
@@ -717,7 +697,7 @@
         </is>
       </c>
       <c r="AA2" s="1" t="n">
-        <v>46108.5328027788</v>
+        <v>46120.379986575</v>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
@@ -726,130 +706,10 @@
       </c>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>5499.63</t>
+          <t>2644.09</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
-        <is>
-          <t>grddeveloper.py@gmail.com</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>May 15 2024</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>Past</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>342125539-00001</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>9964213310</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>$2696.49</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>OSI</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>Verizon</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>USD</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>PO BOX 16810</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>BUILD-A-BEAR WORKSHOP INC</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>7293 BEECHMONT AVE</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>OH</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>45230-4125</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>CINCINNATI</t>
-        </is>
-      </c>
-      <c r="O3" t="inlineStr">
-        <is>
-          <t>United States</t>
-        </is>
-      </c>
-      <c r="S3" t="inlineStr">
-        <is>
-          <t>OX</t>
-        </is>
-      </c>
-      <c r="T3" t="inlineStr">
-        <is>
-          <t>16810</t>
-        </is>
-      </c>
-      <c r="U3" t="inlineStr">
-        <is>
-          <t>PO B</t>
-        </is>
-      </c>
-      <c r="V3" t="inlineStr">
-        <is>
-          <t>United States</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>Approved</t>
-        </is>
-      </c>
-      <c r="AA3" s="1" t="n">
-        <v>46108.53636556549</v>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>Client Admin</t>
-        </is>
-      </c>
-      <c r="AD3" t="inlineStr">
-        <is>
-          <t>2761.63</t>
-        </is>
-      </c>
-      <c r="AF3" t="inlineStr">
         <is>
           <t>grddeveloper.py@gmail.com</t>
         </is>
